--- a/demos/materials/ltc-q2-reimbursement-list.xlsx
+++ b/demos/materials/ltc-q2-reimbursement-list.xlsx
@@ -478,7 +478,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>課堂練習素材 ｜ 大人提 AI Agent 工作坊 2026/06/15 ｜ 模擬數據・全去識別化・僅供課堂練習</t>
+          <t>課堂練習素材 ｜ 長照機構 AI 工具箱（阿峰老師） 2026/06/15 ｜ 模擬數據・全去識別化・僅供課堂練習</t>
         </is>
       </c>
     </row>
@@ -489,6 +489,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -987,8 +988,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
           <t>核銷規定重點（摘）：①單筆 1,000 元以上須附統一發票，收據不可。②所有支出須經據點主任簽核。③估價單不得作為核銷憑證，須換正式發票。④餐費須附參加名冊。</t>
